--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20221.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="50">
   <si>
     <t>Mat</t>
   </si>
@@ -79,25 +79,19 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>TZOMPOLE</t>
   </si>
   <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
     <t>CARRERA</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
   </si>
   <si>
     <t>FLORES</t>
@@ -106,49 +100,28 @@
     <t>ROSAS</t>
   </si>
   <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>FELIPE</t>
-  </si>
-  <si>
-    <t>CASASOLA</t>
+    <t>TEZOCO</t>
   </si>
   <si>
     <t>CAZARES</t>
@@ -157,73 +130,43 @@
     <t>SERRANO</t>
   </si>
   <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>JAIRO YAIR</t>
   </si>
   <si>
     <t>JOSE LEONARDO</t>
   </si>
   <si>
+    <t>GUILLERMO SAUL</t>
+  </si>
+  <si>
+    <t>AZUL MARIAM</t>
+  </si>
+  <si>
+    <t>ZABDIEL</t>
+  </si>
+  <si>
+    <t>JOSE ALONSO</t>
+  </si>
+  <si>
+    <t>CRISTOPHER</t>
+  </si>
+  <si>
+    <t>JOSUE GUSTAVO</t>
+  </si>
+  <si>
+    <t>MICHELLE</t>
+  </si>
+  <si>
+    <t>MARIA DE LOS ANGELES</t>
+  </si>
+  <si>
     <t>MARISOL</t>
-  </si>
-  <si>
-    <t>HAZEL</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>GUILLERMO SAUL</t>
-  </si>
-  <si>
-    <t>ELIDA CITLALI</t>
-  </si>
-  <si>
-    <t>SERGIO IVAN</t>
-  </si>
-  <si>
-    <t>JOSE ALONSO</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>FERNANDA</t>
-  </si>
-  <si>
-    <t>ZAID RAUL</t>
-  </si>
-  <si>
-    <t>MARIA DE LOS ANGELES</t>
-  </si>
-  <si>
-    <t>JOSE</t>
-  </si>
-  <si>
-    <t>ADAMARI</t>
-  </si>
-  <si>
-    <t>ERIK</t>
-  </si>
-  <si>
-    <t>OSCAR</t>
   </si>
 </sst>
 </file>
@@ -624,19 +567,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>58.97</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -650,19 +593,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>85.29000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -676,19 +619,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G4">
-        <v>78.05</v>
+        <v>87.8</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -699,22 +642,22 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G5">
-        <v>60.98</v>
+        <v>85</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -728,10 +671,10 @@
         <v>36</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
         <v>1</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
       </c>
       <c r="F6">
         <v>35</v>
@@ -740,7 +683,7 @@
         <v>97.22</v>
       </c>
       <c r="H6">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -793,16 +736,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>56.41</v>
+      </c>
+      <c r="H2">
+        <v>5.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -816,16 +762,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>88.23999999999999</v>
+      </c>
+      <c r="H3">
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -839,16 +788,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>87.8</v>
+      </c>
+      <c r="H4">
+        <v>6.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -859,19 +811,22 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H5">
+        <v>6.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -885,16 +840,19 @@
         <v>36</v>
       </c>
       <c r="D6">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H6">
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -947,10 +905,10 @@
         <v>39</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>16</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
       </c>
       <c r="F2">
         <v>23</v>
@@ -959,7 +917,7 @@
         <v>58.97</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -973,16 +931,16 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>85.29000000000001</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H3">
         <v>7.2</v>
@@ -999,19 +957,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G4">
-        <v>78.05</v>
+        <v>87.8</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1022,22 +980,22 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>60.98</v>
+        <v>80</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1051,19 +1009,19 @@
         <v>36</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G6">
-        <v>97.22</v>
+        <v>83.33</v>
       </c>
       <c r="H6">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -1073,7 +1031,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1105,16 +1063,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920199</v>
+        <v>22330051920378</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1128,22 +1086,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920217</v>
+        <v>22330051920199</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1151,22 +1109,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920368</v>
+        <v>22330051920402</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1174,22 +1132,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920396</v>
+        <v>22330051920397</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1197,22 +1155,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920402</v>
+        <v>22330051920315</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1220,62 +1178,62 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920420</v>
+        <v>22330051920181</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920265</v>
+        <v>22330051920358</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920181</v>
+        <v>22330051920356</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1289,22 +1247,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920358</v>
+        <v>22330051920224</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1312,22 +1270,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920399</v>
+        <v>22330051920270</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1335,16 +1293,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920260</v>
+        <v>22330051920288</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1353,167 +1311,6 @@
         <v>12</v>
       </c>
       <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920268</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" t="s">
-        <v>63</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920270</v>
-      </c>
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" t="s">
-        <v>64</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920273</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" t="s">
-        <v>65</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920375</v>
-      </c>
-      <c r="B16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" t="s">
-        <v>66</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920276</v>
-      </c>
-      <c r="B17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" t="s">
-        <v>67</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920277</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" t="s">
-        <v>68</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920288</v>
-      </c>
-      <c r="B19" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" t="s">
-        <v>53</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20221.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20221.xlsx
@@ -82,9 +82,15 @@
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
     <t>TZOMPOLE</t>
   </si>
   <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
@@ -100,21 +106,21 @@
     <t>ROSAS</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
     <t>PLIEGO</t>
   </si>
   <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
     <t>COLOHUA</t>
   </si>
   <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -130,18 +136,18 @@
     <t>SERRANO</t>
   </si>
   <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
     <t>JAIRO YAIR</t>
   </si>
   <si>
+    <t>JOSUE GUSTAVO</t>
+  </si>
+  <si>
     <t>JOSE LEONARDO</t>
   </si>
   <si>
+    <t>MICHELLE</t>
+  </si>
+  <si>
     <t>GUILLERMO SAUL</t>
   </si>
   <si>
@@ -155,12 +161,6 @@
   </si>
   <si>
     <t>CRISTOPHER</t>
-  </si>
-  <si>
-    <t>JOSUE GUSTAVO</t>
-  </si>
-  <si>
-    <t>MICHELLE</t>
   </si>
   <si>
     <t>MARIA DE LOS ANGELES</t>
@@ -1086,7 +1086,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920199</v>
+        <v>22330051920356</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
@@ -1109,7 +1109,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920402</v>
+        <v>22330051920199</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
@@ -1124,7 +1124,7 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1132,7 +1132,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920397</v>
+        <v>22330051920224</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
@@ -1147,7 +1147,7 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1155,7 +1155,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920315</v>
+        <v>22330051920402</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -1170,7 +1170,7 @@
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920181</v>
+        <v>22330051920397</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
@@ -1193,15 +1193,15 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920358</v>
+        <v>22330051920315</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
@@ -1216,15 +1216,15 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920356</v>
+        <v>22330051920181</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
@@ -1247,7 +1247,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920224</v>
+        <v>22330051920358</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
@@ -1262,7 +1262,7 @@
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1276,7 +1276,7 @@
         <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
         <v>48</v>
@@ -1299,7 +1299,7 @@
         <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
         <v>49</v>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20221.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20221.xlsx
@@ -736,7 +736,7 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>17</v>
@@ -814,7 +814,7 @@
         <v>40</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>8</v>
@@ -826,7 +826,7 @@
         <v>80</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -840,16 +840,16 @@
         <v>36</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G6">
-        <v>75</v>
+        <v>83.33</v>
       </c>
       <c r="H6">
         <v>6.6</v>
@@ -908,13 +908,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>58.97</v>
+        <v>56.41</v>
       </c>
       <c r="H2">
         <v>6.2</v>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20221.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20221.xlsx
@@ -91,21 +91,21 @@
     <t>SILVESTRE</t>
   </si>
   <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
@@ -121,21 +121,21 @@
     <t>OLIVARES</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>CAZARES</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>CAZARES</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
     <t>JAIRO YAIR</t>
   </si>
   <si>
@@ -148,19 +148,19 @@
     <t>MICHELLE</t>
   </si>
   <si>
+    <t>AZUL MARIAM</t>
+  </si>
+  <si>
+    <t>ZABDIEL</t>
+  </si>
+  <si>
+    <t>JOSE ALONSO</t>
+  </si>
+  <si>
+    <t>CRISTOPHER</t>
+  </si>
+  <si>
     <t>GUILLERMO SAUL</t>
-  </si>
-  <si>
-    <t>AZUL MARIAM</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
-  </si>
-  <si>
-    <t>JOSE ALONSO</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
   </si>
   <si>
     <t>MARIA DE LOS ANGELES</t>
@@ -1155,7 +1155,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920402</v>
+        <v>22330051920397</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -1170,7 +1170,7 @@
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920397</v>
+        <v>22330051920315</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
@@ -1201,7 +1201,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920315</v>
+        <v>22330051920181</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
@@ -1216,15 +1216,15 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920181</v>
+        <v>22330051920358</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
@@ -1247,7 +1247,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920358</v>
+        <v>22330051920402</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
@@ -1262,7 +1262,7 @@
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1276,7 +1276,7 @@
         <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D11" t="s">
         <v>48</v>
@@ -1299,7 +1299,7 @@
         <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
         <v>49</v>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20221.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="52">
   <si>
     <t>Mat</t>
   </si>
@@ -88,6 +88,9 @@
     <t>TZOMPOLE</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>SILVESTRE</t>
   </si>
   <si>
@@ -118,6 +121,9 @@
     <t>COLOHUA</t>
   </si>
   <si>
+    <t>CADENA</t>
+  </si>
+  <si>
     <t>OLIVARES</t>
   </si>
   <si>
@@ -133,9 +139,6 @@
     <t>SERRANO</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>JAIRO YAIR</t>
   </si>
   <si>
@@ -143,6 +146,9 @@
   </si>
   <si>
     <t>JOSE LEONARDO</t>
+  </si>
+  <si>
+    <t>DANA PAOLA</t>
   </si>
   <si>
     <t>MICHELLE</t>
@@ -1031,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1069,10 +1075,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1092,10 +1098,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1115,10 +1121,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1132,16 +1138,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920224</v>
+        <v>22330051920423</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1155,22 +1161,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920397</v>
+        <v>22330051920224</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1178,16 +1184,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920315</v>
+        <v>22330051920397</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1201,39 +1207,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920181</v>
+        <v>22330051920315</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920358</v>
+        <v>22330051920181</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1247,22 +1253,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920402</v>
+        <v>22330051920358</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1270,16 +1276,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920270</v>
+        <v>22330051920402</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1293,16 +1299,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920288</v>
+        <v>22330051920270</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1311,6 +1317,29 @@
         <v>12</v>
       </c>
       <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920288</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20221.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="63">
   <si>
     <t>Mat</t>
   </si>
@@ -79,39 +79,57 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
     <t>RUIZ</t>
   </si>
   <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
     <t>TZOMPOLE</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
     <t>CARRERA</t>
   </si>
   <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
     <t>PLIEGO</t>
   </si>
   <si>
@@ -139,31 +157,46 @@
     <t>SERRANO</t>
   </si>
   <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>FABIAN ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
     <t>JAIRO YAIR</t>
   </si>
   <si>
     <t>JOSUE GUSTAVO</t>
   </si>
   <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>DANA PAOLA</t>
+  </si>
+  <si>
+    <t>MICHELLE</t>
+  </si>
+  <si>
+    <t>AZUL MARIAM</t>
+  </si>
+  <si>
+    <t>ZABDIEL</t>
+  </si>
+  <si>
+    <t>JOSE ALONSO</t>
+  </si>
+  <si>
+    <t>CRISTOPHER</t>
+  </si>
+  <si>
     <t>JOSE LEONARDO</t>
   </si>
   <si>
-    <t>DANA PAOLA</t>
-  </si>
-  <si>
-    <t>MICHELLE</t>
-  </si>
-  <si>
-    <t>AZUL MARIAM</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
-  </si>
-  <si>
-    <t>JOSE ALONSO</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
+    <t>ERIK</t>
   </si>
   <si>
     <t>GUILLERMO SAUL</t>
@@ -745,13 +778,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>56.41</v>
+        <v>58.97</v>
       </c>
       <c r="H2">
         <v>5.9</v>
@@ -914,13 +947,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>56.41</v>
+        <v>58.97</v>
       </c>
       <c r="H2">
         <v>6.2</v>
@@ -1037,7 +1070,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1069,16 +1102,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920378</v>
+        <v>22330051920190</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1092,16 +1125,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920356</v>
+        <v>22330051920413</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1115,16 +1148,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920199</v>
+        <v>22330051920388</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1138,22 +1171,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920423</v>
+        <v>22330051920378</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1161,22 +1194,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920224</v>
+        <v>22330051920356</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1184,22 +1217,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920397</v>
+        <v>22330051920201</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1207,22 +1240,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920315</v>
+        <v>22330051920423</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1230,91 +1263,91 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920181</v>
+        <v>22330051920224</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920358</v>
+        <v>22330051920397</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920402</v>
+        <v>22330051920315</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920270</v>
+        <v>22330051920181</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1322,24 +1355,139 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920288</v>
+        <v>22330051920358</v>
       </c>
       <c r="B13" t="s">
         <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920199</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920202</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920402</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
         <v>12</v>
       </c>
-      <c r="G13">
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920270</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920288</v>
+      </c>
+      <c r="B18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20221.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="58">
   <si>
     <t>Mat</t>
   </si>
@@ -82,9 +82,6 @@
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
@@ -94,78 +91,69 @@
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>TZOMPOLE</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>JORGE</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>TZOMPOLE</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>CADENA</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>CAZARES</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
     <t>ARACELY</t>
   </si>
   <si>
-    <t>FABIAN ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
     <t>JAIRO YAIR</t>
   </si>
   <si>
@@ -175,37 +163,34 @@
     <t>ALEXANDER</t>
   </si>
   <si>
-    <t>DANA PAOLA</t>
-  </si>
-  <si>
     <t>MICHELLE</t>
   </si>
   <si>
+    <t>NIDIA GABRIELA</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>AGUSTIN ARTURO</t>
+  </si>
+  <si>
     <t>AZUL MARIAM</t>
   </si>
   <si>
     <t>ZABDIEL</t>
   </si>
   <si>
-    <t>JOSE ALONSO</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
     <t>JOSE LEONARDO</t>
   </si>
   <si>
-    <t>ERIK</t>
+    <t>KARLA YARITZY</t>
   </si>
   <si>
     <t>GUILLERMO SAUL</t>
   </si>
   <si>
-    <t>MARIA DE LOS ANGELES</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
+    <t>ABDIEL ARMANDO</t>
   </si>
 </sst>
 </file>
@@ -947,16 +932,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>58.97</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -973,16 +958,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>88.23999999999999</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -999,16 +984,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>87.8</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1034,7 +1019,7 @@
         <v>80</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1051,16 +1036,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G6">
-        <v>83.33</v>
+        <v>80.56</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
@@ -1070,7 +1055,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1108,10 +1093,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1125,16 +1110,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920413</v>
+        <v>22330051920378</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1148,16 +1133,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920388</v>
+        <v>22330051920356</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1171,16 +1156,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920378</v>
+        <v>22330051920201</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1194,22 +1179,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920356</v>
+        <v>22330051920224</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1217,22 +1202,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920201</v>
+        <v>22330051920369</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1240,22 +1225,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920423</v>
+        <v>21330051920396</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1263,22 +1248,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920224</v>
+        <v>22330051920274</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1289,13 +1274,13 @@
         <v>22330051920397</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1312,13 +1297,13 @@
         <v>22330051920315</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1332,16 +1317,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920181</v>
+        <v>22330051920199</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1355,22 +1340,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920358</v>
+        <v>22330051920374</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1378,22 +1363,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920199</v>
+        <v>22330051920402</v>
       </c>
       <c r="B14" t="s">
         <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1401,93 +1386,24 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920202</v>
+        <v>22330051920302</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
         <v>39</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920402</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920270</v>
-      </c>
-      <c r="B17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920288</v>
-      </c>
-      <c r="B18" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" t="s">
-        <v>62</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20221.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20221.xlsx
@@ -85,33 +85,33 @@
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
     <t>RUIZ</t>
   </si>
   <si>
+    <t>TZOMPOLE</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>TZOMPOLE</t>
-  </si>
-  <si>
     <t>CARRERA</t>
   </si>
   <si>
@@ -124,27 +124,27 @@
     <t>PLIEGO</t>
   </si>
   <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
     <t>ALFONSO</t>
   </si>
   <si>
     <t>COLOHUA</t>
   </si>
   <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
     <t>JORGE</t>
   </si>
   <si>
@@ -157,31 +157,31 @@
     <t>JAIRO YAIR</t>
   </si>
   <si>
+    <t>MICHELLE</t>
+  </si>
+  <si>
+    <t>NIDIA GABRIELA</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>AGUSTIN ARTURO</t>
+  </si>
+  <si>
+    <t>AZUL MARIAM</t>
+  </si>
+  <si>
+    <t>ZABDIEL</t>
+  </si>
+  <si>
     <t>JOSUE GUSTAVO</t>
   </si>
   <si>
+    <t>JOSE LEONARDO</t>
+  </si>
+  <si>
     <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>MICHELLE</t>
-  </si>
-  <si>
-    <t>NIDIA GABRIELA</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>AGUSTIN ARTURO</t>
-  </si>
-  <si>
-    <t>AZUL MARIAM</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
-  </si>
-  <si>
-    <t>JOSE LEONARDO</t>
   </si>
   <si>
     <t>KARLA YARITZY</t>
@@ -1133,7 +1133,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920356</v>
+        <v>22330051920224</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
@@ -1148,7 +1148,7 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1156,13 +1156,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920201</v>
+        <v>22330051920369</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
         <v>47</v>
@@ -1171,7 +1171,7 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1179,13 +1179,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920224</v>
+        <v>21330051920396</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
         <v>48</v>
@@ -1194,7 +1194,7 @@
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1202,13 +1202,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920369</v>
+        <v>22330051920274</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
         <v>49</v>
@@ -1217,7 +1217,7 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1225,7 +1225,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920396</v>
+        <v>22330051920397</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
@@ -1240,7 +1240,7 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1248,7 +1248,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920274</v>
+        <v>22330051920315</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
@@ -1263,7 +1263,7 @@
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1271,7 +1271,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920397</v>
+        <v>22330051920356</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
@@ -1286,15 +1286,15 @@
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920315</v>
+        <v>22330051920199</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
@@ -1309,21 +1309,21 @@
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920199</v>
+        <v>22330051920201</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
         <v>54</v>
@@ -1343,7 +1343,7 @@
         <v>22330051920374</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
         <v>42</v>
@@ -1392,7 +1392,7 @@
         <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D15" t="s">
         <v>57</v>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20221.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="57">
   <si>
     <t>Mat</t>
   </si>
@@ -88,36 +88,36 @@
     <t>SILVESTRE</t>
   </si>
   <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>TZOMPOLE</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>VENTURA</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>TZOMPOLE</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>CIRUELO</t>
   </si>
   <si>
@@ -130,27 +130,27 @@
     <t>SOTO</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>JORGE</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>TEZOCO</t>
   </si>
   <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>ARACELY</t>
   </si>
   <si>
@@ -160,37 +160,34 @@
     <t>MICHELLE</t>
   </si>
   <si>
-    <t>NIDIA GABRIELA</t>
-  </si>
-  <si>
     <t>IGNACIO</t>
   </si>
   <si>
-    <t>AGUSTIN ARTURO</t>
+    <t>GUILLERMO SAUL</t>
+  </si>
+  <si>
+    <t>JONATHAN YAEL</t>
   </si>
   <si>
     <t>AZUL MARIAM</t>
   </si>
   <si>
+    <t>JOSUE GUSTAVO</t>
+  </si>
+  <si>
+    <t>JOSE LEONARDO</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>KARLA YARITZY</t>
+  </si>
+  <si>
+    <t>ABDIEL ARMANDO</t>
+  </si>
+  <si>
     <t>ZABDIEL</t>
-  </si>
-  <si>
-    <t>JOSUE GUSTAVO</t>
-  </si>
-  <si>
-    <t>JOSE LEONARDO</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>KARLA YARITZY</t>
-  </si>
-  <si>
-    <t>GUILLERMO SAUL</t>
-  </si>
-  <si>
-    <t>ABDIEL ARMANDO</t>
   </si>
 </sst>
 </file>
@@ -1055,7 +1052,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1156,13 +1153,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920369</v>
+        <v>21330051920396</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
         <v>47</v>
@@ -1171,7 +1168,7 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1179,13 +1176,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920396</v>
+        <v>22330051920402</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
         <v>48</v>
@@ -1202,13 +1199,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920274</v>
+        <v>22330051920403</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
         <v>49</v>
@@ -1248,7 +1245,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920315</v>
+        <v>22330051920356</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
@@ -1263,15 +1260,15 @@
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920356</v>
+        <v>22330051920199</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
@@ -1294,13 +1291,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920199</v>
+        <v>22330051920201</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
         <v>53</v>
@@ -1317,7 +1314,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920201</v>
+        <v>22330051920374</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
@@ -1332,7 +1329,7 @@
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1340,10 +1337,10 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920374</v>
+        <v>22330051920302</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
         <v>42</v>
@@ -1355,7 +1352,7 @@
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1363,10 +1360,10 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920402</v>
+        <v>22330051920315</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
         <v>43</v>
@@ -1378,32 +1375,9 @@
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920302</v>
-      </c>
-      <c r="B15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" t="s">
-        <v>57</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20221.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="65">
   <si>
     <t>Mat</t>
   </si>
@@ -88,33 +88,42 @@
     <t>SILVESTRE</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>TZOMPOLE</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
     <t>ARIAS</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>SANTOS</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>TZOMPOLE</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>VENTURA</t>
   </si>
   <si>
@@ -127,24 +136,27 @@
     <t>OLIVARES</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>GALINDO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>JORGE</t>
+  </si>
+  <si>
     <t>SOTO</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -160,31 +172,43 @@
     <t>MICHELLE</t>
   </si>
   <si>
+    <t>NIDIA GABRIELA</t>
+  </si>
+  <si>
+    <t>GUILLERMO SAUL</t>
+  </si>
+  <si>
+    <t>JONATHAN YAEL</t>
+  </si>
+  <si>
+    <t>BRANDON</t>
+  </si>
+  <si>
+    <t>MIRIAM AIMAR</t>
+  </si>
+  <si>
+    <t>FRANCISCO</t>
+  </si>
+  <si>
+    <t>JOSUE GUSTAVO</t>
+  </si>
+  <si>
+    <t>JOSE LEONARDO</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>KARLA YARITZY</t>
+  </si>
+  <si>
     <t>IGNACIO</t>
   </si>
   <si>
-    <t>GUILLERMO SAUL</t>
-  </si>
-  <si>
-    <t>JONATHAN YAEL</t>
+    <t>ABDIEL ARMANDO</t>
   </si>
   <si>
     <t>AZUL MARIAM</t>
-  </si>
-  <si>
-    <t>JOSUE GUSTAVO</t>
-  </si>
-  <si>
-    <t>JOSE LEONARDO</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>KARLA YARITZY</t>
-  </si>
-  <si>
-    <t>ABDIEL ARMANDO</t>
   </si>
   <si>
     <t>ZABDIEL</t>
@@ -1052,7 +1076,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1090,10 +1114,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1113,10 +1137,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1136,10 +1160,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1153,22 +1177,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920396</v>
+        <v>22330051920369</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1182,10 +1206,10 @@
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1208,7 +1232,7 @@
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1222,22 +1246,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920397</v>
+        <v>22330051920395</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1245,7 +1269,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920356</v>
+        <v>22330051920370</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
@@ -1254,53 +1278,53 @@
         <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920199</v>
+        <v>22330051920418</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920201</v>
+        <v>22330051920356</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1314,22 +1338,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920374</v>
+        <v>22330051920199</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1337,22 +1361,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920302</v>
+        <v>22330051920201</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1360,24 +1384,116 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
+        <v>22330051920374</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920396</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920302</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920397</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
         <v>22330051920315</v>
       </c>
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
         <v>13</v>
       </c>
-      <c r="G14">
+      <c r="G18">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20221.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="71">
   <si>
     <t>Mat</t>
   </si>
@@ -85,36 +85,42 @@
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>USCANGA</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>TZOMPOLE</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>SILVESTRE</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>TZOMPOLE</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
     <t>ARIAS</t>
   </si>
   <si>
@@ -133,27 +139,33 @@
     <t>PLIEGO</t>
   </si>
   <si>
+    <t>JUAN</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>GALINDO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>JORGE</t>
+  </si>
+  <si>
     <t>OLIVARES</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>GALINDO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
     <t>SOTO</t>
   </si>
   <si>
@@ -169,37 +181,43 @@
     <t>JAIRO YAIR</t>
   </si>
   <si>
+    <t>EMILIANO DE JESUS</t>
+  </si>
+  <si>
+    <t>NIDIA GABRIELA</t>
+  </si>
+  <si>
+    <t>GUILLERMO SAUL</t>
+  </si>
+  <si>
+    <t>JONATHAN YAEL</t>
+  </si>
+  <si>
+    <t>BRANDON</t>
+  </si>
+  <si>
+    <t>MIRIAM AIMAR</t>
+  </si>
+  <si>
+    <t>FRANCISCO</t>
+  </si>
+  <si>
+    <t>JOSUE GUSTAVO</t>
+  </si>
+  <si>
+    <t>JOSE LEONARDO</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>ANDREA</t>
+  </si>
+  <si>
+    <t>KARLA YARITZY</t>
+  </si>
+  <si>
     <t>MICHELLE</t>
-  </si>
-  <si>
-    <t>NIDIA GABRIELA</t>
-  </si>
-  <si>
-    <t>GUILLERMO SAUL</t>
-  </si>
-  <si>
-    <t>JONATHAN YAEL</t>
-  </si>
-  <si>
-    <t>BRANDON</t>
-  </si>
-  <si>
-    <t>MIRIAM AIMAR</t>
-  </si>
-  <si>
-    <t>FRANCISCO</t>
-  </si>
-  <si>
-    <t>JOSUE GUSTAVO</t>
-  </si>
-  <si>
-    <t>JOSE LEONARDO</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>KARLA YARITZY</t>
   </si>
   <si>
     <t>IGNACIO</t>
@@ -1076,7 +1094,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1114,10 +1132,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1137,10 +1155,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1154,16 +1172,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920224</v>
+        <v>22330051920365</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1183,10 +1201,10 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1206,10 +1224,10 @@
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1232,7 +1250,7 @@
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1252,10 +1270,10 @@
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1275,10 +1293,10 @@
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1298,10 +1316,10 @@
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1321,10 +1339,10 @@
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1344,10 +1362,10 @@
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1367,10 +1385,10 @@
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1384,16 +1402,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920374</v>
+        <v>22330051920210</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1407,22 +1425,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920396</v>
+        <v>22330051920374</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1430,22 +1448,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920302</v>
+        <v>22330051920224</v>
       </c>
       <c r="B16" t="s">
         <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1453,22 +1471,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920397</v>
+        <v>21330051920396</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1476,16 +1494,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920315</v>
+        <v>22330051920302</v>
       </c>
       <c r="B18" t="s">
         <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1494,6 +1512,52 @@
         <v>13</v>
       </c>
       <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>22330051920397</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>22330051920315</v>
+      </c>
+      <c r="B20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" t="s">
+        <v>70</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20221.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="79">
   <si>
     <t>Mat</t>
   </si>
@@ -88,6 +88,12 @@
     <t>USCANGA</t>
   </si>
   <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>GALICIA</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
@@ -100,6 +106,9 @@
     <t>ROMERO</t>
   </si>
   <si>
+    <t>LIBRADO</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
@@ -142,12 +151,21 @@
     <t>JUAN</t>
   </si>
   <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
     <t>GALINDO</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
@@ -169,9 +187,6 @@
     <t>SOTO</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>TEZOCO</t>
   </si>
   <si>
@@ -184,6 +199,12 @@
     <t>EMILIANO DE JESUS</t>
   </si>
   <si>
+    <t>FERNANDA MARGARITA</t>
+  </si>
+  <si>
+    <t>KARLOS ARATH</t>
+  </si>
+  <si>
     <t>NIDIA GABRIELA</t>
   </si>
   <si>
@@ -194,6 +215,9 @@
   </si>
   <si>
     <t>BRANDON</t>
+  </si>
+  <si>
+    <t>LESLIE YAMILET</t>
   </si>
   <si>
     <t>MIRIAM AIMAR</t>
@@ -1094,7 +1118,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1132,10 +1156,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1155,10 +1179,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1178,10 +1202,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1195,16 +1219,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920369</v>
+        <v>22330051920233</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1218,22 +1242,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920402</v>
+        <v>22330051920422</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1241,22 +1265,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920403</v>
+        <v>22330051920369</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1264,16 +1288,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920395</v>
+        <v>22330051920402</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1287,22 +1311,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920370</v>
+        <v>22330051920403</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1310,22 +1334,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920418</v>
+        <v>22330051920395</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1333,91 +1357,91 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920356</v>
+        <v>22330051920417</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920199</v>
+        <v>22330051920370</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920201</v>
+        <v>22330051920418</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920210</v>
+        <v>22330051920356</v>
       </c>
       <c r="B14" t="s">
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1425,22 +1449,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920374</v>
+        <v>22330051920199</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1448,22 +1472,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920224</v>
+        <v>22330051920201</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1471,22 +1495,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920396</v>
+        <v>22330051920210</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1494,22 +1518,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920302</v>
+        <v>22330051920374</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D18" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1517,22 +1541,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920397</v>
+        <v>22330051920224</v>
       </c>
       <c r="B19" t="s">
         <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1540,24 +1564,93 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920315</v>
+        <v>21330051920396</v>
       </c>
       <c r="B20" t="s">
         <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D20" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>22330051920302</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
         <v>13</v>
       </c>
-      <c r="G20">
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>22330051920397</v>
+      </c>
+      <c r="B22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>22330051920315</v>
+      </c>
+      <c r="B23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" t="s">
+        <v>78</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23">
         <v>1</v>
       </c>
     </row>
